--- a/Logbook Aaron Austen.xlsx
+++ b/Logbook Aaron Austen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Magang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059425B6-2225-4DEE-8738-73DFD5D4BA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DDA151-1197-428F-976D-25AAA633BD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F04DFA45-EC09-44DA-998B-1A5C85F74496}"/>
   </bookViews>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
   <si>
     <t>Logbook Acitivity</t>
   </si>
@@ -250,13 +250,46 @@
   </si>
   <si>
     <t>membuat login page menggunakan flutter dan firebase</t>
+  </si>
+  <si>
+    <t>merangkai sensor ketinggian air</t>
+  </si>
+  <si>
+    <t>merangkai sensor RFID</t>
+  </si>
+  <si>
+    <t>membuat sistem rfid, mengubungkan dengan baterai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menghubungkan sensor dengan </t>
+  </si>
+  <si>
+    <t>Menghubungkan website dengan database</t>
+  </si>
+  <si>
+    <t>Menghubungkan login page dengan firebase</t>
+  </si>
+  <si>
+    <t>09.00</t>
+  </si>
+  <si>
+    <t>Merapikan sistem IoT dan menghubungkan dengan database</t>
+  </si>
+  <si>
+    <t>menghubungkan sistem IoT dengan database</t>
+  </si>
+  <si>
+    <t>Memperlajari MQTT dan mengimplementasikan dengan sensor</t>
+  </si>
+  <si>
+    <t>menghubungkan MQTT dengan sensor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +307,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -320,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -336,6 +376,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -656,9 +717,9 @@
   <sheetFormatPr defaultColWidth="14.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -696,16 +757,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -714,15 +775,15 @@
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8" s="11">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -731,15 +792,15 @@
       <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="11">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -748,15 +809,15 @@
       <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10" s="11">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -765,246 +826,286 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11" s="11">
         <v>5</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="A12" s="11">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13" s="11">
         <v>7</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="3"/>
+      <c r="D13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14" s="11">
         <v>8</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="3"/>
+      <c r="D14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15" s="11">
         <v>9</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16" s="11">
         <v>10</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17" s="11">
         <v>11</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="B17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18" s="11">
         <v>12</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19" s="11">
         <v>13</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20" s="11">
         <v>14</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="1"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21" s="11">
         <v>15</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="1"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22" s="11">
         <v>16</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23" s="11">
         <v>17</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="11">
         <v>18</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="1"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="11">
         <v>19</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="1"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="11">
         <v>20</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="1"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27" s="11">
         <v>21</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="1"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28" s="11">
         <v>22</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="1"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29" s="11">
         <v>23</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30" s="11">
         <v>24</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="1"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31" s="11">
         <v>25</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32" s="11">
         <v>26</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33" s="11">
         <v>27</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34" s="11">
         <v>28</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="1"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
